--- a/SGI_Sistema-de-gestao-integrado/SGI_Sistema-de-gestao-da-qualidade/Registos_SGQ_Plasticom/SGQ-19_Melhoria_Continua_Custo_Qualidade.xlsx
+++ b/SGI_Sistema-de-gestao-integrado/SGI_Sistema-de-gestao-da-qualidade/Registos_SGQ_Plasticom/SGQ-19_Melhoria_Continua_Custo_Qualidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project Portfolios\manufacturing-performance-analytics\SGI_Sistema-de-gestao-integrado\SGI_Sistema-de-gestao-da-qualidade\Registos_SGQ_Plasticom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AA9122B-A235-4650-A28C-B38A6A7F8FD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68D896D3-FC60-4BF1-AC44-3E02BE14A776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2489,7 +2489,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-47F9-4DE6-84F2-91C4A507DBE3}"/>
+              <c16:uniqueId val="{00000000-2A87-456C-BC3C-7B8CFF8C2B58}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2640,7 +2640,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-47F9-4DE6-84F2-91C4A507DBE3}"/>
+              <c16:uniqueId val="{00000001-2A87-456C-BC3C-7B8CFF8C2B58}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2791,7 +2791,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-47F9-4DE6-84F2-91C4A507DBE3}"/>
+              <c16:uniqueId val="{00000002-2A87-456C-BC3C-7B8CFF8C2B58}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2942,7 +2942,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-47F9-4DE6-84F2-91C4A507DBE3}"/>
+              <c16:uniqueId val="{00000003-2A87-456C-BC3C-7B8CFF8C2B58}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
